--- a/docs/Шаблон_справочников.xlsx
+++ b/docs/Шаблон_справочников.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Подразделения" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Пользователи" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Статьи бюджета" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Категории" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Номенклатура" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Поставщики" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Рамочные договоры" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Пороги согласования" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Станции" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Подразделения" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Пользователи" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Статьи бюджета" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Категории" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Номенклатура" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Поставщики" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Рамочные договоры" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Коридоры согласования" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -165,12 +166,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Уникальное название</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Согласует СЗ подразделения. Логин с листа «Пользователи»</t>
+        <t>Станции/филиалы</t>
       </text>
     </comment>
   </commentList>
@@ -185,22 +181,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Латиница, без пробелов. Лучше как в AD/почте</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Для уведомлений</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Точно как на листе «Подразделения»</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Через запятую: Инициатор, Согласующий, Закупщик, Директор, Финдиректор, Бухгалтер, Администратор</t>
+        <t>Уникальное название</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Согласует СЗ подразделения. Логин с листа «Пользователи»</t>
       </text>
     </comment>
   </commentList>
@@ -215,7 +201,27 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Как в бюджете / 1С</t>
+        <t>Латиница, без пробелов. Лучше как в AD/почте</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Для уведомлений</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Точно как на листе «Подразделения»</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Как на листе «Станции»</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Через запятую: Инициатор, Руководитель подразделения, Закупки (ОМТС), Главный инженер, Финансы (ФЭО), Юристы (ЮО), Генеральный директор, ПТО, Бухгалтерия, Администратор</t>
       </text>
     </comment>
   </commentList>
@@ -230,7 +236,12 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Группа закупок; по ней подбираются поставщики</t>
+        <t>Как в бюджете / 1С</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Для показа остатка по статье, ₸</t>
       </text>
     </comment>
   </commentList>
@@ -243,19 +254,9 @@
     <author>Шаблон</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>шт, пач, уп, кг, л, м, усл …</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Как на листе «Категории»</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Код номенклатуры в 1С — ключ сопоставления поступлений</t>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Группа закупок; по ней подбираются поставщики</t>
       </text>
     </comment>
   </commentList>
@@ -270,22 +271,17 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>12 цифр. Ключ поиска при повторной загрузке</t>
+        <t>шт, пач, уп, кг, л, м, усл …</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Куда отправлять запросы КП</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Через точку с запятой</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Код контрагента в 1С</t>
+        <t>Как на листе «Категории»</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Код номенклатуры в 1С — ключ сопоставления поступлений</t>
       </text>
     </comment>
   </commentList>
@@ -300,12 +296,22 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>ДД.ММ.ГГГГ</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>ДД.ММ.ГГГГ</t>
+        <t>12 цифр. Ключ поиска при повторной загрузке</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Куда отправлять запросы КП</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Через точку с запятой</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Код контрагента в 1С</t>
       </text>
     </comment>
   </commentList>
@@ -318,14 +324,49 @@
     <author>Шаблон</author>
   </authors>
   <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>ДД.ММ.ГГГГ</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>ДД.ММ.ГГГГ</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Шаблон</author>
+  </authors>
+  <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Сумма решения по закупке, ₸</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Директор / Финдиректор</t>
+        <t>g / y / r / simple</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Верхняя граница, ₸. Пусто — без границы</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Через запятую, названия ролей</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Рабочих дней</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>да — упрощённый круг для закупок по договору</t>
       </text>
     </comment>
   </commentList>
@@ -621,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -675,7 +716,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Роли: Инициатор, Согласующий, Закупщик, Директор, Финдиректор, Бухгалтер, Администратор</t>
+          <t>Роли: Инициатор, Руководитель подразделения, Закупки (ОМТС), Главный инженер, Финансы (ФЭО), Юристы (ЮО), Генеральный директор, ПТО, Бухгалтерия, Администратор</t>
         </is>
       </c>
     </row>
@@ -692,56 +733,63 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Подразделения: Наименование: IT-отдел | Руководитель (логин): saparova</t>
+          <t>Станции: Наименование: ГРЭС-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Пользователи: Логин: ivanov | Фамилия: Иванов | Имя: Иван | E-mail: ivanov@company.kz | Подразделение: IT-отдел | Должность: Системный администратор | Роли: Инициатор</t>
+          <t>Подразделения: Наименование: IT-отдел | Руководитель (логин): saparova</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Статьи бюджета: Код: 01.01 | Наименование: Канцелярские расходы</t>
+          <t>Пользователи: Логин: ivanov | Фамилия: Иванов | Имя: Иван | E-mail: ivanov@company.kz | Подразделение: IT-отдел | Должность: Инженер КТЦ | Станция: ГРЭС-1 | Роли: Инициатор</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Категории: Наименование: Канцтовары</t>
+          <t>Статьи бюджета: Код: 01.01 | Наименование: Ремонт основного оборудования | Лимит на год: 250000000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Номенклатура: Наименование: Бумага А4 SvetoCopy, 500 л. | Ед. изм.: пач | Категория: Канцтовары | Код 1С: 00-0001</t>
+          <t>Категории: Наименование: Канцтовары</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Поставщики: Наименование: ТОО «Канцлер» | БИН/ИИН: 180540012345 | E-mail: sales@kancler.kz | Телефон: +7 727 000 00 00 | Контактное лицо: Асель | Категории: Канцтовары; Хозтовары | Код 1С: 000123</t>
+          <t>Номенклатура: Наименование: Бумага А4 SvetoCopy, 500 л. | Ед. изм.: пач | Категория: Канцтовары | Код 1С: 00-0001</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Рамочные договоры: Номер: РД-2026-001 | Дата: 15.01.2026 | Поставщик (БИН или наименование): 180540012345 | Действует до: 31.12.2026</t>
+          <t>Поставщики: Наименование: ТОО «Канцлер» | БИН/ИИН: 180540012345 | E-mail: sales@kancler.kz | Телефон: +7 727 000 00 00 | Контактное лицо: Асель | Категории: Канцтовары; Хозтовары | Код 1С: 000123</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Пороги согласования: Сумма от: 1000000 | Роль: Директор</t>
+          <t>Рамочные договоры: Номер: РД-2026-001 | Дата: 15.01.2026 | Поставщик (БИН или наименование): 180540012345 | Действует до: 31.12.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Коридоры согласования: Код: g | Название: Зелёный | Сумма до: 5000000 | Согласующие роли: Главный инженер | Срок, р.д.: 1 | По действующему договору: </t>
         </is>
       </c>
     </row>
@@ -750,7 +798,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Код *</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Название *</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Сумма до</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Согласующие роли *</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Срок, р.д. *</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>По действующему договору</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Наименование *</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -781,13 +909,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -797,6 +925,7 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -830,7 +959,12 @@
           <t>Должность</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Станция</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Роли *</t>
         </is>
@@ -842,17 +976,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,6 +1001,11 @@
           <t>Наименование *</t>
         </is>
       </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Лимит на год</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -873,7 +1013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -898,7 +1038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -941,7 +1081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1002,7 +1142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1043,35 +1183,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Сумма от *</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Роль *</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>